--- a/output/Data and Chart Outputs/au_gas_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_prices.xlsx
@@ -191,12 +191,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$8</f>
+              <f>'Chart'!$E$2:$E$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$8</f>
+              <f>'Chart'!$B$2:$B$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$8</f>
+              <f>'Chart'!$E$2:$E$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$8</f>
+              <f>'Chart'!$C$2:$C$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -263,12 +263,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$8</f>
+              <f>'Chart'!$E$2:$E$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$8</f>
+              <f>'Chart'!$D$2:$D$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -709,7 +709,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 03 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
+          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 05 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -885,6 +885,34 @@
       </c>
       <c r="D8" t="n">
         <v>11.094</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B9" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11.63</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B10" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="C10" t="n">
+        <v>11.6944</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.832</v>
       </c>
     </row>
   </sheetData>
@@ -899,7 +927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1022,6 +1050,34 @@
         <v>11.094</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B9" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11.63</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B10" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="C10" t="n">
+        <v>11.6944</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.832</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/au_gas_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_prices.xlsx
@@ -191,12 +191,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$10</f>
+              <f>'Chart'!$E$2:$E$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$10</f>
+              <f>'Chart'!$B$2:$B$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$10</f>
+              <f>'Chart'!$E$2:$E$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$10</f>
+              <f>'Chart'!$C$2:$C$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -263,12 +263,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$10</f>
+              <f>'Chart'!$E$2:$E$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$10</f>
+              <f>'Chart'!$D$2:$D$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -709,7 +709,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 05 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
+          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 06 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -913,6 +913,20 @@
       </c>
       <c r="D10" t="n">
         <v>11.832</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B11" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>11.992</v>
+      </c>
+      <c r="D11" t="n">
+        <v>12.059</v>
       </c>
     </row>
   </sheetData>
@@ -927,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1078,6 +1092,20 @@
         <v>11.832</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B11" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>11.992</v>
+      </c>
+      <c r="D11" t="n">
+        <v>12.059</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/au_gas_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_prices.xlsx
@@ -191,12 +191,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$11</f>
+              <f>'Chart'!$E$2:$E$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$11</f>
+              <f>'Chart'!$B$2:$B$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$11</f>
+              <f>'Chart'!$E$2:$E$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$11</f>
+              <f>'Chart'!$C$2:$C$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -263,12 +263,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$11</f>
+              <f>'Chart'!$E$2:$E$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$11</f>
+              <f>'Chart'!$D$2:$D$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -709,7 +709,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 06 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
+          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 07 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -927,6 +927,20 @@
       </c>
       <c r="D11" t="n">
         <v>12.059</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B12" t="n">
+        <v>12.125</v>
+      </c>
+      <c r="C12" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="D12" t="n">
+        <v>12.6</v>
       </c>
     </row>
   </sheetData>
@@ -941,7 +955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1106,6 +1120,20 @@
         <v>12.059</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B12" t="n">
+        <v>12.125</v>
+      </c>
+      <c r="C12" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="D12" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/au_gas_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_prices.xlsx
@@ -191,12 +191,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$12</f>
+              <f>'Chart'!$E$2:$E$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$12</f>
+              <f>'Chart'!$B$2:$B$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$12</f>
+              <f>'Chart'!$E$2:$E$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$12</f>
+              <f>'Chart'!$C$2:$C$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -263,12 +263,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$12</f>
+              <f>'Chart'!$E$2:$E$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$12</f>
+              <f>'Chart'!$D$2:$D$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -709,7 +709,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 07 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
+          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 08 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -941,6 +941,20 @@
       </c>
       <c r="D12" t="n">
         <v>12.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B13" t="n">
+        <v>12.3525</v>
+      </c>
+      <c r="C13" t="n">
+        <v>12.514</v>
+      </c>
+      <c r="D13" t="n">
+        <v>12.8525</v>
       </c>
     </row>
   </sheetData>
@@ -955,7 +969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1134,6 +1148,20 @@
         <v>12.6</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B13" t="n">
+        <v>12.3525</v>
+      </c>
+      <c r="C13" t="n">
+        <v>12.514</v>
+      </c>
+      <c r="D13" t="n">
+        <v>12.8525</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/au_gas_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_prices.xlsx
@@ -155,6 +155,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Australia east coast gas hub prices, STTM ex-ante (AEMO) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -191,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$13</f>
+              <f>'Chart'!$E$2:$E$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$13</f>
+              <f>'Chart'!$B$2:$B$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -227,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$13</f>
+              <f>'Chart'!$E$2:$E$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$13</f>
+              <f>'Chart'!$C$2:$C$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -263,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$13</f>
+              <f>'Chart'!$E$2:$E$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$13</f>
+              <f>'Chart'!$D$2:$D$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -709,7 +710,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 08 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
+          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 09 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
         </is>
       </c>
     </row>
@@ -746,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -955,6 +956,20 @@
       </c>
       <c r="D13" t="n">
         <v>12.8525</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B14" t="n">
+        <v>12.1143</v>
+      </c>
+      <c r="C14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>12.83</v>
       </c>
     </row>
   </sheetData>
@@ -969,7 +984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1162,6 +1177,20 @@
         <v>12.8525</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B14" t="n">
+        <v>12.1143</v>
+      </c>
+      <c r="C14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>12.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/au_gas_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_prices.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$14</f>
+              <f>'Chart'!$E$2:$E$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$14</f>
+              <f>'Chart'!$B$2:$B$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$14</f>
+              <f>'Chart'!$E$2:$E$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$14</f>
+              <f>'Chart'!$C$2:$C$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -264,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$14</f>
+              <f>'Chart'!$E$2:$E$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$14</f>
+              <f>'Chart'!$D$2:$D$15</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 09 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
+          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 10 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -970,6 +970,20 @@
       </c>
       <c r="D14" t="n">
         <v>12.83</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B15" t="n">
+        <v>11.655</v>
+      </c>
+      <c r="C15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>11.3</v>
       </c>
     </row>
   </sheetData>
@@ -984,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1191,6 +1205,20 @@
         <v>12.83</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B15" t="n">
+        <v>11.655</v>
+      </c>
+      <c r="C15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/au_gas_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_prices.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$15</f>
+              <f>'Chart'!$E$2:$E$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$15</f>
+              <f>'Chart'!$B$2:$B$16</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$15</f>
+              <f>'Chart'!$E$2:$E$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$15</f>
+              <f>'Chart'!$C$2:$C$16</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -264,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$15</f>
+              <f>'Chart'!$E$2:$E$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$15</f>
+              <f>'Chart'!$D$2:$D$16</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 10 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
+          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 11 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -984,6 +984,20 @@
       </c>
       <c r="D15" t="n">
         <v>11.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1219,6 +1233,20 @@
         <v>11.3</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/au_gas_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_prices.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$16</f>
+              <f>'Chart'!$E$2:$E$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$16</f>
+              <f>'Chart'!$B$2:$B$17</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$16</f>
+              <f>'Chart'!$E$2:$E$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$16</f>
+              <f>'Chart'!$C$2:$C$17</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -264,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$16</f>
+              <f>'Chart'!$E$2:$E$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$16</f>
+              <f>'Chart'!$D$2:$D$17</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 11 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
+          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 12 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -998,6 +998,20 @@
       </c>
       <c r="D16" t="n">
         <v>11.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="C17" t="n">
+        <v>11.2988</v>
+      </c>
+      <c r="D17" t="n">
+        <v>11.6505</v>
       </c>
     </row>
   </sheetData>
@@ -1012,7 +1026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1247,6 +1261,20 @@
         <v>11.1</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="C17" t="n">
+        <v>11.2988</v>
+      </c>
+      <c r="D17" t="n">
+        <v>11.6505</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/au_gas_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_prices.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$17</f>
+              <f>'Chart'!$E$2:$E$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$17</f>
+              <f>'Chart'!$B$2:$B$24</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$17</f>
+              <f>'Chart'!$E$2:$E$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$17</f>
+              <f>'Chart'!$C$2:$C$24</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -264,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$17</f>
+              <f>'Chart'!$E$2:$E$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$17</f>
+              <f>'Chart'!$D$2:$D$24</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 12 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
+          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 29 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1012,6 +1012,104 @@
       </c>
       <c r="D17" t="n">
         <v>11.6505</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B18" t="n">
+        <v>11.9215</v>
+      </c>
+      <c r="C18" t="n">
+        <v>12.0208</v>
+      </c>
+      <c r="D18" t="n">
+        <v>12.071</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B19" t="n">
+        <v>11.8899</v>
+      </c>
+      <c r="C19" t="n">
+        <v>11.9521</v>
+      </c>
+      <c r="D19" t="n">
+        <v>12.1532</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B20" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="C20" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="D20" t="n">
+        <v>12.4025</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B21" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="C21" t="n">
+        <v>12.4025</v>
+      </c>
+      <c r="D21" t="n">
+        <v>12.48</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B22" t="n">
+        <v>12.3987</v>
+      </c>
+      <c r="C22" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="D22" t="n">
+        <v>12.7015</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B23" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="C23" t="n">
+        <v>12.5525</v>
+      </c>
+      <c r="D23" t="n">
+        <v>12.58</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B24" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="C24" t="n">
+        <v>12.2387</v>
+      </c>
+      <c r="D24" t="n">
+        <v>12.7515</v>
       </c>
     </row>
   </sheetData>
@@ -1026,7 +1124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1275,6 +1373,104 @@
         <v>11.6505</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B18" t="n">
+        <v>11.9215</v>
+      </c>
+      <c r="C18" t="n">
+        <v>12.0208</v>
+      </c>
+      <c r="D18" t="n">
+        <v>12.071</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B19" t="n">
+        <v>11.8899</v>
+      </c>
+      <c r="C19" t="n">
+        <v>11.9521</v>
+      </c>
+      <c r="D19" t="n">
+        <v>12.1532</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B20" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="C20" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="D20" t="n">
+        <v>12.4025</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B21" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="C21" t="n">
+        <v>12.4025</v>
+      </c>
+      <c r="D21" t="n">
+        <v>12.48</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B22" t="n">
+        <v>12.3987</v>
+      </c>
+      <c r="C22" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="D22" t="n">
+        <v>12.7015</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B23" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="C23" t="n">
+        <v>12.5525</v>
+      </c>
+      <c r="D23" t="n">
+        <v>12.58</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B24" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="C24" t="n">
+        <v>12.2387</v>
+      </c>
+      <c r="D24" t="n">
+        <v>12.7515</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/au_gas_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_prices.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$24</f>
+              <f>'Chart'!$E$2:$E$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$24</f>
+              <f>'Chart'!$B$2:$B$25</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$24</f>
+              <f>'Chart'!$E$2:$E$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$24</f>
+              <f>'Chart'!$C$2:$C$25</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -264,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$24</f>
+              <f>'Chart'!$E$2:$E$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$24</f>
+              <f>'Chart'!$D$2:$D$25</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 29 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
+          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 30 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1110,6 +1110,20 @@
       </c>
       <c r="D24" t="n">
         <v>12.7515</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>12</v>
+      </c>
+      <c r="D25" t="n">
+        <v>12.5959</v>
       </c>
     </row>
   </sheetData>
@@ -1124,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1471,6 +1485,20 @@
         <v>12.7515</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>12</v>
+      </c>
+      <c r="D25" t="n">
+        <v>12.5959</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/au_gas_prices.xlsx
+++ b/output/Data and Chart Outputs/au_gas_prices.xlsx
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$25</f>
+              <f>'Chart'!$E$2:$E$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$25</f>
+              <f>'Chart'!$B$2:$B$26</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$25</f>
+              <f>'Chart'!$E$2:$E$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$25</f>
+              <f>'Chart'!$C$2:$C$26</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -264,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$25</f>
+              <f>'Chart'!$E$2:$E$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$25</f>
+              <f>'Chart'!$D$2:$D$26</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -710,7 +710,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 30 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
+          <t>Sydney, Adelaide and Brisbane STTM hubs, daily, 27 Sep 2026 to 31 Oct 2026. History builds from the first run (the report is a rolling window). The Victorian DWGM price is not included yet.</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1124,6 +1124,20 @@
       </c>
       <c r="D25" t="n">
         <v>12.5959</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B26" t="n">
+        <v>12.097</v>
+      </c>
+      <c r="C26" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2988</v>
       </c>
     </row>
   </sheetData>
@@ -1138,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1499,6 +1513,20 @@
         <v>12.5959</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B26" t="n">
+        <v>12.097</v>
+      </c>
+      <c r="C26" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2988</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
